--- a/outputs/reports/easy_ensemble_v2/evaluation.xlsx
+++ b/outputs/reports/easy_ensemble_v2/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7652640516476455</v>
+        <v>0.7990145228215768</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01048170554171654</v>
+        <v>0.01570079142200664</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7632508833922261</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02067942110385984</v>
+        <v>0.03076538269134567</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7652706099034975</v>
+        <v>0.7991822490754726</v>
       </c>
       <c r="G2" t="n">
-        <v>199441</v>
+        <v>30687</v>
       </c>
       <c r="H2" t="n">
-        <v>61174</v>
+        <v>7711</v>
       </c>
       <c r="I2" t="n">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="J2" t="n">
-        <v>648</v>
+        <v>123</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8544423088930242</v>
+        <v>0.8636376058681039</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04277795762859236</v>
+        <v>0.07784826065444765</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07265774378585087</v>
+        <v>0.08808290155440414</v>
       </c>
       <c r="E2" t="n">
-        <v>22.37618883536362</v>
+        <v>20.96590545640632</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2237926972909305</v>
+        <v>0.2098765432098765</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0289123451124369</v>
+        <v>0.04512448132780083</v>
       </c>
       <c r="I2" t="n">
-        <v>8.904048766169849</v>
+        <v>10.74074074074074</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4452296819787986</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01939036983210311</v>
+        <v>0.02982365145228216</v>
       </c>
       <c r="M2" t="n">
-        <v>5.971594414347476</v>
+        <v>7.098765432098766</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5971731448763251</v>
+        <v>0.7098765432098766</v>
       </c>
     </row>
   </sheetData>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1476</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45406</v>
+        <v>7156</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001101176056027838</v>
+        <v>0.0001397428731134712</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -768,13 +768,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>152035</v>
+        <v>23452</v>
       </c>
       <c r="C6" t="n">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001282599401453613</v>
+        <v>0.001620330888623572</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59952</v>
+        <v>7816</v>
       </c>
       <c r="C7" t="n">
-        <v>459</v>
+        <v>101</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007656124899919936</v>
+        <v>0.01292221084953941</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2381</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>159</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06677866442671146</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -825,16 +825,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>214</v>
-      </c>
-      <c r="C9" t="n">
-        <v>31</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1448598130841121</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
